--- a/data/K총무 포켓북.xlsx
+++ b/data/K총무 포켓북.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\J\Desktop\K총무 E포켓북\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F0F627-2848-429B-971A-58788E2C7A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E60936-A2AC-46A9-818F-72C832361BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" tabRatio="897" xr2:uid="{B28B0413-8E3E-49EF-A856-28E8B55E2C38}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" tabRatio="897" activeTab="1" xr2:uid="{B28B0413-8E3E-49EF-A856-28E8B55E2C38}"/>
   </bookViews>
   <sheets>
     <sheet name="조직도" sheetId="3" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="492">
   <si>
     <t>조직도</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -581,10 +581,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>회으실 번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>인원수</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1977,6 +1973,14 @@
   </si>
   <si>
     <t>Level</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>직급</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의실 번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2426,6 +2430,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2433,6 +2440,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2444,15 +2460,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2461,9 +2468,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2795,23 +2799,23 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="45" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -2824,11 +2828,11 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="45" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -2838,14 +2842,14 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="45" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -2855,14 +2859,14 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="45" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -2872,14 +2876,14 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="45" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -2889,14 +2893,14 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="45" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2906,10 +2910,10 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2942,28 +2946,28 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>163</v>
-      </c>
       <c r="H2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I2"/>
     </row>
@@ -2975,7 +2979,7 @@
         <v>117</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2994,11 +2998,11 @@
         <v>117</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2">
@@ -3015,11 +3019,11 @@
         <v>117</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2">
@@ -3036,11 +3040,11 @@
         <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2">
@@ -3057,11 +3061,11 @@
         <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2">
@@ -3078,11 +3082,11 @@
         <v>117</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2">
@@ -3099,7 +3103,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -3118,7 +3122,7 @@
         <v>117</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -3135,7 +3139,7 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -3152,7 +3156,7 @@
         <v>117</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -3190,30 +3194,30 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>123</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>213</v>
-      </c>
       <c r="G2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H2"/>
     </row>
@@ -3228,10 +3232,10 @@
         <v>15</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -3245,13 +3249,13 @@
         <v>117</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -3262,16 +3266,16 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -3282,16 +3286,16 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -3302,16 +3306,16 @@
         <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -3322,16 +3326,16 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -3342,16 +3346,16 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -3365,13 +3369,13 @@
         <v>118</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -3385,13 +3389,13 @@
         <v>118</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -3405,13 +3409,13 @@
         <v>118</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -3425,13 +3429,13 @@
         <v>119</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -3445,13 +3449,13 @@
         <v>119</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -3465,13 +3469,13 @@
         <v>119</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -3485,13 +3489,13 @@
         <v>120</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -3505,13 +3509,13 @@
         <v>120</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -3525,13 +3529,13 @@
         <v>120</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -3545,13 +3549,13 @@
         <v>121</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -3565,13 +3569,13 @@
         <v>121</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -3585,13 +3589,13 @@
         <v>121</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -3605,13 +3609,13 @@
         <v>122</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -3625,13 +3629,13 @@
         <v>122</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -3645,13 +3649,13 @@
         <v>122</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -3665,13 +3669,13 @@
         <v>117</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -3685,13 +3689,13 @@
         <v>117</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -3705,13 +3709,13 @@
         <v>117</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -3725,13 +3729,13 @@
         <v>117</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -3745,13 +3749,13 @@
         <v>118</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -3765,13 +3769,13 @@
         <v>118</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -3785,13 +3789,13 @@
         <v>118</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -3805,13 +3809,13 @@
         <v>118</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -3825,13 +3829,13 @@
         <v>119</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -3845,13 +3849,13 @@
         <v>119</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -3865,13 +3869,13 @@
         <v>119</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -3885,13 +3889,13 @@
         <v>120</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -3905,13 +3909,13 @@
         <v>120</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -3925,13 +3929,13 @@
         <v>120</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -3945,13 +3949,13 @@
         <v>121</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -3965,13 +3969,13 @@
         <v>121</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -3985,13 +3989,13 @@
         <v>121</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -4005,13 +4009,13 @@
         <v>122</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -4025,13 +4029,13 @@
         <v>122</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -4045,13 +4049,13 @@
         <v>122</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -4085,7 +4089,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4093,16 +4097,16 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="E2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4115,10 +4119,10 @@
         <v>15</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3"/>
@@ -4129,13 +4133,13 @@
         <v>117</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4"/>
@@ -4143,16 +4147,16 @@
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5"/>
@@ -4160,16 +4164,16 @@
     </row>
     <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6"/>
@@ -4177,16 +4181,16 @@
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7"/>
@@ -4194,16 +4198,16 @@
     </row>
     <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8"/>
@@ -4211,16 +4215,16 @@
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9"/>
@@ -4231,13 +4235,13 @@
         <v>118</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10"/>
@@ -4248,13 +4252,13 @@
         <v>118</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11"/>
@@ -4265,13 +4269,13 @@
         <v>118</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12"/>
@@ -4282,13 +4286,13 @@
         <v>119</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13"/>
@@ -4299,13 +4303,13 @@
         <v>119</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14"/>
@@ -4316,13 +4320,13 @@
         <v>119</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15"/>
@@ -4333,13 +4337,13 @@
         <v>120</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16"/>
@@ -4350,13 +4354,13 @@
         <v>120</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17"/>
@@ -4367,13 +4371,13 @@
         <v>120</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18"/>
@@ -4384,13 +4388,13 @@
         <v>121</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19"/>
@@ -4401,13 +4405,13 @@
         <v>121</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20"/>
@@ -4418,13 +4422,13 @@
         <v>121</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21"/>
@@ -4435,13 +4439,13 @@
         <v>122</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22"/>
@@ -4474,27 +4478,27 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>123</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="F2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2"/>
     </row>
@@ -4506,13 +4510,13 @@
         <v>118</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3"/>
@@ -4525,13 +4529,13 @@
         <v>118</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4"/>
@@ -4544,13 +4548,13 @@
         <v>118</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>260</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5"/>
@@ -4563,13 +4567,13 @@
         <v>119</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6"/>
@@ -4582,13 +4586,13 @@
         <v>119</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7"/>
@@ -4601,13 +4605,13 @@
         <v>119</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>260</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8"/>
@@ -4620,13 +4624,13 @@
         <v>120</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9"/>
@@ -4639,13 +4643,13 @@
         <v>120</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10"/>
@@ -4658,13 +4662,13 @@
         <v>121</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11"/>
@@ -4677,13 +4681,13 @@
         <v>121</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12"/>
@@ -4696,13 +4700,13 @@
         <v>122</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13"/>
@@ -4715,13 +4719,13 @@
         <v>122</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14"/>
@@ -4753,7 +4757,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4761,32 +4765,32 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="E2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3"/>
@@ -4800,10 +4804,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4"/>
@@ -4814,13 +4818,13 @@
         <v>117</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5"/>
@@ -4831,13 +4835,13 @@
         <v>117</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6"/>
@@ -4848,13 +4852,13 @@
         <v>117</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7"/>
@@ -4865,13 +4869,13 @@
         <v>117</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8"/>
@@ -4882,13 +4886,13 @@
         <v>117</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9"/>
@@ -4899,13 +4903,13 @@
         <v>117</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10"/>
@@ -4916,13 +4920,13 @@
         <v>117</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11"/>
@@ -4933,13 +4937,13 @@
         <v>117</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12"/>
@@ -4947,16 +4951,16 @@
     </row>
     <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13"/>
@@ -4964,16 +4968,16 @@
     </row>
     <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14"/>
@@ -4981,16 +4985,16 @@
     </row>
     <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B15" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15"/>
@@ -4998,16 +5002,16 @@
     </row>
     <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16"/>
@@ -5015,16 +5019,16 @@
     </row>
     <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17"/>
@@ -5032,16 +5036,16 @@
     </row>
     <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18"/>
@@ -5049,16 +5053,16 @@
     </row>
     <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19"/>
@@ -5066,16 +5070,16 @@
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20"/>
@@ -5083,16 +5087,16 @@
     </row>
     <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21"/>
@@ -5100,16 +5104,16 @@
     </row>
     <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22"/>
@@ -5142,7 +5146,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -5150,16 +5154,16 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="E2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5169,35 +5173,35 @@
         <v>117</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
@@ -5207,16 +5211,16 @@
         <v>118</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F5"/>
       <c r="G5"/>
@@ -5226,16 +5230,16 @@
         <v>118</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C6" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F6"/>
       <c r="G6"/>
@@ -5245,16 +5249,16 @@
         <v>119</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C7" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F7"/>
       <c r="G7"/>
@@ -5264,16 +5268,16 @@
         <v>119</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F8"/>
       <c r="G8"/>
@@ -5283,16 +5287,16 @@
         <v>120</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
@@ -5302,16 +5306,16 @@
         <v>120</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C10" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
@@ -5321,16 +5325,16 @@
         <v>121</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C11" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>
@@ -5340,16 +5344,16 @@
         <v>121</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C12" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F12"/>
       <c r="G12"/>
@@ -5359,16 +5363,16 @@
         <v>122</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C13" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F13"/>
       <c r="G13"/>
@@ -5378,16 +5382,16 @@
         <v>122</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C14" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F14"/>
       <c r="G14"/>
@@ -5397,16 +5401,16 @@
         <v>122</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C15" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="F15"/>
       <c r="G15"/>
@@ -5439,7 +5443,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -5447,92 +5451,92 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="E2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B3" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F5"/>
       <c r="G5"/>
     </row>
     <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="F6"/>
       <c r="G6"/>
@@ -5565,7 +5569,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -5573,73 +5577,73 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>212</v>
-      </c>
       <c r="E2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="F5"/>
       <c r="G5"/>
@@ -5673,7 +5677,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -5681,93 +5685,93 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E3"/>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E4"/>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -5798,21 +5802,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>123</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E2"/>
     </row>
@@ -5824,10 +5828,10 @@
         <v>117</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E3"/>
     </row>
@@ -5839,10 +5843,10 @@
         <v>117</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E4"/>
     </row>
@@ -5854,10 +5858,10 @@
         <v>117</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E5"/>
     </row>
@@ -5866,13 +5870,13 @@
         <v>89</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E6"/>
     </row>
@@ -5894,12 +5898,12 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:F95"/>
+  <dimension ref="B1:F94"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="113.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="109.125" style="5" customWidth="1"/>
@@ -5927,7 +5931,7 @@
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="2:6" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -5939,9 +5943,11 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="2:6" ht="330" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="46"/>
-      <c r="C4" s="45" t="s">
+    <row r="4" spans="2:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -5953,8 +5959,12 @@
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
@@ -5964,8 +5974,12 @@
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="D6" s="2" t="s">
         <v>74</v>
       </c>
@@ -5974,9 +5988,11 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="2:6" ht="313.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="46"/>
-      <c r="C7" s="45" t="s">
+    <row r="7" spans="2:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -5988,8 +6004,12 @@
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
+      <c r="B8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
@@ -5999,8 +6019,12 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D9" s="2" t="s">
         <v>74</v>
       </c>
@@ -6009,9 +6033,11 @@
       </c>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="2:6" ht="313.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="46"/>
-      <c r="C10" s="45" t="s">
+    <row r="10" spans="2:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -6023,8 +6049,12 @@
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="D11" s="2" t="s">
         <v>23</v>
       </c>
@@ -6034,8 +6064,12 @@
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="46"/>
-      <c r="C12" s="47"/>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="D12" s="2" t="s">
         <v>74</v>
       </c>
@@ -6044,9 +6078,11 @@
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="2:6" ht="214.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="46"/>
-      <c r="C13" s="45" t="s">
+    <row r="13" spans="2:6" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -6058,8 +6094,12 @@
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
+      <c r="B14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="D14" s="2" t="s">
         <v>23</v>
       </c>
@@ -6069,8 +6109,12 @@
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="46"/>
-      <c r="C15" s="47"/>
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="D15" s="2" t="s">
         <v>74</v>
       </c>
@@ -6080,7 +6124,9 @@
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="46"/>
+      <c r="B16" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
@@ -6093,8 +6139,10 @@
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="2:6" ht="132" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="46"/>
-      <c r="C17" s="45" t="s">
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -6106,8 +6154,12 @@
       <c r="F17" s="1"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="D18" s="2" t="s">
         <v>74</v>
       </c>
@@ -6117,7 +6169,9 @@
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="46"/>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C19" s="2" t="s">
         <v>28</v>
       </c>
@@ -6130,7 +6184,9 @@
       <c r="F19" s="1"/>
     </row>
     <row r="20" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="46"/>
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C20" s="2" t="s">
         <v>92</v>
       </c>
@@ -6143,7 +6199,9 @@
       <c r="F20" s="1"/>
     </row>
     <row r="21" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="46"/>
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
@@ -6153,8 +6211,10 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="2:6" ht="198" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="47"/>
+    <row r="22" spans="2:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C22" s="2" t="s">
         <v>90</v>
       </c>
@@ -6165,7 +6225,7 @@
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="52" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -6178,7 +6238,7 @@
       <c r="F23" s="1"/>
     </row>
     <row r="24" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="49"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="2" t="s">
         <v>52</v>
       </c>
@@ -6188,8 +6248,8 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="2:6" ht="148.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="49"/>
+    <row r="25" spans="2:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="B25" s="53"/>
       <c r="C25" s="2" t="s">
         <v>53</v>
       </c>
@@ -6200,7 +6260,7 @@
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="50"/>
+      <c r="B26" s="54"/>
       <c r="C26" s="2" t="s">
         <v>85</v>
       </c>
@@ -6211,7 +6271,7 @@
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="46" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="10" t="s">
@@ -6221,12 +6281,12 @@
         <v>64</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="46"/>
+      <c r="B28" s="47"/>
       <c r="C28" s="2" t="s">
         <v>65</v>
       </c>
@@ -6237,7 +6297,7 @@
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="46"/>
+      <c r="B29" s="47"/>
       <c r="C29" s="2" t="s">
         <v>66</v>
       </c>
@@ -6246,7 +6306,7 @@
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="47"/>
+      <c r="B30" s="48"/>
       <c r="C30" s="2" t="s">
         <v>67</v>
       </c>
@@ -6256,8 +6316,8 @@
       </c>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="2:6" ht="165" x14ac:dyDescent="0.3">
-      <c r="B31" s="45" t="s">
+    <row r="31" spans="2:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="B31" s="46" t="s">
         <v>58</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -6271,8 +6331,8 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="2:6" ht="264" x14ac:dyDescent="0.3">
-      <c r="B32" s="46"/>
+    <row r="32" spans="2:6" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B32" s="47"/>
       <c r="C32" s="2" t="s">
         <v>114</v>
       </c>
@@ -6283,7 +6343,7 @@
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="46" t="s">
         <v>84</v>
       </c>
       <c r="C33" s="10" t="s">
@@ -6296,16 +6356,20 @@
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="46"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="E34" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45" t="s">
+      <c r="B35" s="46" t="s">
         <v>86</v>
       </c>
       <c r="C35" s="10" t="s">
@@ -6318,16 +6382,20 @@
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="46"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="E36" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="46" t="s">
         <v>55</v>
       </c>
       <c r="C37" s="3" t="s">
@@ -6338,7 +6406,7 @@
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="46"/>
+      <c r="B38" s="47"/>
       <c r="C38" s="3" t="s">
         <v>109</v>
       </c>
@@ -6349,7 +6417,7 @@
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="46" t="s">
         <v>56</v>
       </c>
       <c r="C39" s="10" t="s">
@@ -6362,7 +6430,7 @@
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="46"/>
+      <c r="B40" s="47"/>
       <c r="C40" s="3" t="s">
         <v>105</v>
       </c>
@@ -6373,7 +6441,7 @@
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="46" t="s">
         <v>33</v>
       </c>
       <c r="C41" s="10" t="s">
@@ -6384,8 +6452,8 @@
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="46"/>
-      <c r="C42" s="45" t="s">
+      <c r="B42" s="47"/>
+      <c r="C42" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -6397,8 +6465,10 @@
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="D43" s="2" t="s">
         <v>40</v>
       </c>
@@ -6408,8 +6478,10 @@
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="D44" s="2" t="s">
         <v>39</v>
       </c>
@@ -6419,8 +6491,10 @@
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="46"/>
-      <c r="C45" s="47"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="D45" s="12" t="s">
         <v>74</v>
       </c>
@@ -6430,8 +6504,8 @@
       <c r="F45" s="1"/>
     </row>
     <row r="46" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="46"/>
-      <c r="C46" s="45" t="s">
+      <c r="B46" s="47"/>
+      <c r="C46" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -6443,8 +6517,10 @@
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D47" s="2" t="s">
         <v>40</v>
       </c>
@@ -6454,8 +6530,10 @@
       <c r="F47" s="1"/>
     </row>
     <row r="48" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D48" s="2" t="s">
         <v>39</v>
       </c>
@@ -6465,8 +6543,10 @@
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D49" s="12" t="s">
         <v>74</v>
       </c>
@@ -6476,7 +6556,7 @@
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="45" t="s">
+      <c r="B50" s="46" t="s">
         <v>44</v>
       </c>
       <c r="C50" s="10" t="s">
@@ -6489,7 +6569,7 @@
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="46"/>
+      <c r="B51" s="47"/>
       <c r="C51" s="10" t="s">
         <v>76</v>
       </c>
@@ -6500,7 +6580,7 @@
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="46"/>
+      <c r="B52" s="47"/>
       <c r="C52" s="2" t="s">
         <v>36</v>
       </c>
@@ -6508,12 +6588,12 @@
         <v>36</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="46"/>
+      <c r="B53" s="47"/>
       <c r="C53" s="2" t="s">
         <v>74</v>
       </c>
@@ -6526,7 +6606,7 @@
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="47"/>
+      <c r="B54" s="48"/>
       <c r="C54" s="2" t="s">
         <v>69</v>
       </c>
@@ -6535,7 +6615,7 @@
       <c r="F54" s="1"/>
     </row>
     <row r="55" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="45" t="s">
+      <c r="B55" s="46" t="s">
         <v>46</v>
       </c>
       <c r="C55" s="10" t="s">
@@ -6548,7 +6628,7 @@
       <c r="F55" s="1"/>
     </row>
     <row r="56" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="46"/>
+      <c r="B56" s="47"/>
       <c r="C56" s="10" t="s">
         <v>76</v>
       </c>
@@ -6559,7 +6639,7 @@
       <c r="F56" s="1"/>
     </row>
     <row r="57" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="46"/>
+      <c r="B57" s="47"/>
       <c r="C57" s="2" t="s">
         <v>36</v>
       </c>
@@ -6567,12 +6647,12 @@
         <v>36</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F57" s="1"/>
     </row>
     <row r="58" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="46"/>
+      <c r="B58" s="47"/>
       <c r="C58" s="2" t="s">
         <v>74</v>
       </c>
@@ -6585,7 +6665,7 @@
       <c r="F58" s="1"/>
     </row>
     <row r="59" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="46"/>
+      <c r="B59" s="47"/>
       <c r="C59" s="2" t="s">
         <v>69</v>
       </c>
@@ -6594,7 +6674,7 @@
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="45" t="s">
+      <c r="B60" s="46" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="10" t="s">
@@ -6607,7 +6687,7 @@
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="46"/>
+      <c r="B61" s="47"/>
       <c r="C61" s="10" t="s">
         <v>76</v>
       </c>
@@ -6618,7 +6698,7 @@
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="46"/>
+      <c r="B62" s="47"/>
       <c r="C62" s="2" t="s">
         <v>36</v>
       </c>
@@ -6626,12 +6706,12 @@
         <v>36</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F62" s="1"/>
     </row>
     <row r="63" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="46"/>
+      <c r="B63" s="47"/>
       <c r="C63" s="2" t="s">
         <v>74</v>
       </c>
@@ -6644,7 +6724,7 @@
       <c r="F63" s="1"/>
     </row>
     <row r="64" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="47"/>
+      <c r="B64" s="48"/>
       <c r="C64" s="2" t="s">
         <v>69</v>
       </c>
@@ -6653,7 +6733,7 @@
       <c r="F64" s="1"/>
     </row>
     <row r="65" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="45" t="s">
+      <c r="B65" s="46" t="s">
         <v>80</v>
       </c>
       <c r="C65" s="10" t="s">
@@ -6666,7 +6746,7 @@
       <c r="F65" s="1"/>
     </row>
     <row r="66" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="46"/>
+      <c r="B66" s="47"/>
       <c r="C66" s="10" t="s">
         <v>76</v>
       </c>
@@ -6677,7 +6757,7 @@
       <c r="F66" s="1"/>
     </row>
     <row r="67" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="46"/>
+      <c r="B67" s="47"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
       <c r="E67" s="15" t="s">
@@ -6686,7 +6766,7 @@
       <c r="F67" s="1"/>
     </row>
     <row r="68" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="46"/>
+      <c r="B68" s="47"/>
       <c r="C68" s="2" t="s">
         <v>36</v>
       </c>
@@ -6694,12 +6774,12 @@
         <v>36</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="46"/>
+      <c r="B69" s="47"/>
       <c r="C69" s="2" t="s">
         <v>74</v>
       </c>
@@ -6712,364 +6792,361 @@
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="47"/>
-      <c r="C70" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D70" s="2"/>
-      <c r="E70" s="7"/>
+      <c r="B70" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E70" s="11"/>
       <c r="F70" s="1"/>
     </row>
     <row r="71" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="C71" s="10" t="s">
+      <c r="B71" s="47"/>
+      <c r="C71" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="48"/>
+      <c r="C72" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D73" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="1"/>
-    </row>
-    <row r="72" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="46"/>
-      <c r="C72" s="2" t="s">
+      <c r="E73" s="11"/>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="47"/>
+      <c r="C74" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="F72" s="1"/>
-    </row>
-    <row r="73" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="47"/>
-      <c r="C73" s="2" t="s">
+      <c r="E74" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="48"/>
+      <c r="C75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D75" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E73" s="13" t="s">
+      <c r="E75" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F73" s="1"/>
-    </row>
-    <row r="74" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C74" s="10" t="s">
+      <c r="F75" s="1"/>
+    </row>
+    <row r="76" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C76" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D76" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E74" s="11"/>
-      <c r="F74" s="1"/>
-    </row>
-    <row r="75" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="46"/>
-      <c r="C75" s="2" t="s">
+      <c r="E76" s="11"/>
+      <c r="F76" s="1"/>
+    </row>
+    <row r="77" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="47"/>
+      <c r="C77" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="F75" s="1"/>
-    </row>
-    <row r="76" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="47"/>
-      <c r="C76" s="2" t="s">
+      <c r="E77" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F77" s="1"/>
+    </row>
+    <row r="78" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="48"/>
+      <c r="C78" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D78" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E78" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F76" s="1"/>
-    </row>
-    <row r="77" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E77" s="11"/>
-      <c r="F77" s="1"/>
-    </row>
-    <row r="78" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="46"/>
-      <c r="C78" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>465</v>
-      </c>
       <c r="F78" s="1"/>
     </row>
     <row r="79" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="47"/>
+      <c r="B79" s="46" t="s">
+        <v>89</v>
+      </c>
       <c r="C79" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B80" s="48"/>
+      <c r="C80" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D80" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E79" s="13" t="s">
+      <c r="E80" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F79" s="1"/>
-    </row>
-    <row r="80" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2" t="s">
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E81" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B82" s="48"/>
+      <c r="C82" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B83" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B84" s="47"/>
+      <c r="C84" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B85" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F80" s="1"/>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B81" s="47"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="12" t="s">
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B86" s="48"/>
+      <c r="C86" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E81" s="13" t="s">
+      <c r="D86" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B87" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B88" s="48"/>
+      <c r="C88" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E88" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F81" s="1"/>
-    </row>
-    <row r="82" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F82" s="1"/>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B83" s="47"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="12" t="s">
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B90" s="50"/>
+      <c r="C90" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E83" s="13" t="s">
+      <c r="D90" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F83" s="1"/>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B84" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F84" s="1"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="46"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="12" t="s">
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D91" s="2"/>
+      <c r="E91" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="50"/>
+      <c r="C92" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E85" s="13" t="s">
+      <c r="D92" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E92" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F85" s="1"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B86" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="1"/>
-    </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B87" s="47"/>
-      <c r="C87" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F87" s="1"/>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B88" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F88" s="1"/>
-    </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B89" s="47"/>
-      <c r="C89" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F89" s="1"/>
-    </row>
-    <row r="90" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D90" s="2"/>
-      <c r="E90" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F90" s="1"/>
-    </row>
-    <row r="91" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="53"/>
-      <c r="C91" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="F91" s="1"/>
-    </row>
-    <row r="92" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="7" t="s">
-        <v>88</v>
-      </c>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B93" s="53"/>
+    <row r="93" spans="2:6" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B93" s="51" t="s">
+        <v>16</v>
+      </c>
       <c r="C93" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="2:6" ht="379.5" x14ac:dyDescent="0.3">
-      <c r="B94" s="51" t="s">
-        <v>16</v>
-      </c>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B94" s="51"/>
       <c r="C94" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B95" s="51"/>
-      <c r="C95" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F95" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="B3:B22"/>
+  <mergeCells count="23">
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B41:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B65:B69"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="B79:B80"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="B37:B38"/>
     <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="B60:B64"/>
-    <mergeCell ref="B65:B70"/>
-    <mergeCell ref="B71:B73"/>
     <mergeCell ref="B23:B26"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B41:B49"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C17:C18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7090,26 +7167,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
       <c r="E2"/>
     </row>
-    <row r="3" spans="1:5" ht="132" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
@@ -7140,43 +7217,43 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>320</v>
-      </c>
       <c r="H2" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
     </row>
     <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -7196,7 +7273,7 @@
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -7218,7 +7295,7 @@
     </row>
     <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -7238,7 +7315,7 @@
     </row>
     <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -7258,7 +7335,7 @@
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -7278,7 +7355,7 @@
     </row>
     <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -7300,7 +7377,7 @@
     </row>
     <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -7320,7 +7397,7 @@
     </row>
     <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
@@ -7342,7 +7419,7 @@
     </row>
     <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7362,7 +7439,7 @@
     </row>
     <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2">
@@ -7432,39 +7509,39 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="I2" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>291</v>
-      </c>
       <c r="J2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K2"/>
     </row>
@@ -7473,7 +7550,7 @@
         <v>92</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -7495,7 +7572,7 @@
         <v>92</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -7519,7 +7596,7 @@
         <v>92</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -7541,7 +7618,7 @@
         <v>92</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2">
@@ -7563,7 +7640,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -7585,7 +7662,7 @@
         <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -7605,7 +7682,7 @@
         <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -7627,7 +7704,7 @@
         <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -7649,7 +7726,7 @@
         <v>92</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -7671,7 +7748,7 @@
         <v>92</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2">
@@ -7693,7 +7770,7 @@
         <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2">
@@ -7717,7 +7794,7 @@
         <v>92</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -7739,7 +7816,7 @@
         <v>92</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -7763,7 +7840,7 @@
         <v>92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -7785,7 +7862,7 @@
         <v>92</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -7809,7 +7886,7 @@
         <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -7831,7 +7908,7 @@
         <v>92</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -7851,7 +7928,7 @@
         <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2">
@@ -7920,24 +7997,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2"/>
     </row>
-    <row r="3" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3"/>
     </row>
@@ -7972,10 +8049,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2"/>
     </row>
@@ -7984,7 +8061,7 @@
         <v>82</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C3"/>
     </row>
@@ -8019,10 +8096,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2"/>
     </row>
@@ -8031,7 +8108,7 @@
         <v>83</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C3"/>
     </row>
@@ -8066,19 +8143,19 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2"/>
     </row>
-    <row r="3" spans="1:3" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C3"/>
     </row>
@@ -8104,7 +8181,7 @@
   <sheetData>
     <row r="1" spans="1:33" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -8213,7 +8290,7 @@
       <c r="B5" s="29"/>
       <c r="C5" s="30"/>
       <c r="D5" s="33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E5" s="31"/>
       <c r="F5" s="30"/>
@@ -9118,7 +9195,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -9151,101 +9228,101 @@
     <row r="3" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="29"/>
       <c r="C3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E3" s="30"/>
       <c r="F3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H3" s="30"/>
       <c r="I3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K3" s="30"/>
       <c r="L3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N3" s="30"/>
       <c r="O3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q3" s="30"/>
       <c r="R3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="T3" s="30"/>
       <c r="U3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="W3" s="30"/>
       <c r="X3" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Z3" s="32"/>
     </row>
     <row r="4" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="29"/>
       <c r="C4" s="31" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D4" s="31"/>
       <c r="E4" s="30"/>
       <c r="F4" s="31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G4" s="31"/>
       <c r="H4" s="30"/>
       <c r="I4" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J4" s="31"/>
       <c r="K4" s="30"/>
       <c r="L4" s="31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M4" s="31"/>
       <c r="N4" s="30"/>
       <c r="O4" s="31" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P4" s="31"/>
       <c r="Q4" s="30"/>
       <c r="R4" s="31" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="S4" s="31"/>
       <c r="T4" s="30"/>
       <c r="U4" s="31" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="V4" s="31"/>
       <c r="W4" s="30"/>
       <c r="X4" s="31" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y4" s="31"/>
       <c r="Z4" s="32"/>
@@ -9253,42 +9330,42 @@
     <row r="5" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="29"/>
       <c r="C5" s="31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D5" s="31"/>
       <c r="E5" s="30"/>
       <c r="F5" s="31" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G5" s="31"/>
       <c r="H5" s="30"/>
       <c r="I5" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J5" s="31"/>
       <c r="K5" s="30"/>
       <c r="L5" s="31" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M5" s="31"/>
       <c r="N5" s="30"/>
       <c r="O5" s="31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P5" s="31"/>
       <c r="Q5" s="30"/>
       <c r="R5" s="31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="S5" s="31"/>
       <c r="T5" s="30"/>
       <c r="U5" s="31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="V5" s="31"/>
       <c r="W5" s="30"/>
       <c r="X5" s="31" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Y5" s="31"/>
       <c r="Z5" s="32"/>
@@ -9296,42 +9373,42 @@
     <row r="6" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="29"/>
       <c r="C6" s="31" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D6" s="31"/>
       <c r="E6" s="30"/>
       <c r="F6" s="31" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G6" s="31"/>
       <c r="H6" s="30"/>
       <c r="I6" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J6" s="31"/>
       <c r="K6" s="30"/>
       <c r="L6" s="31" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M6" s="31"/>
       <c r="N6" s="30"/>
       <c r="O6" s="31" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P6" s="31"/>
       <c r="Q6" s="30"/>
       <c r="R6" s="31" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="S6" s="31"/>
       <c r="T6" s="30"/>
       <c r="U6" s="31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="V6" s="31"/>
       <c r="W6" s="30"/>
       <c r="X6" s="31" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Y6" s="31"/>
       <c r="Z6" s="32"/>
@@ -9339,42 +9416,42 @@
     <row r="7" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="29"/>
       <c r="C7" s="31" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D7" s="31"/>
       <c r="E7" s="30"/>
       <c r="F7" s="31" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G7" s="31"/>
       <c r="H7" s="30"/>
       <c r="I7" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J7" s="31"/>
       <c r="K7" s="30"/>
       <c r="L7" s="31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M7" s="31"/>
       <c r="N7" s="30"/>
       <c r="O7" s="31" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P7" s="31"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="31" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="S7" s="31"/>
       <c r="T7" s="30"/>
       <c r="U7" s="31" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="V7" s="31"/>
       <c r="W7" s="30"/>
       <c r="X7" s="31" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Y7" s="31"/>
       <c r="Z7" s="32"/>
@@ -9382,42 +9459,42 @@
     <row r="8" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="29"/>
       <c r="C8" s="31" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D8" s="31"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G8" s="31"/>
       <c r="H8" s="30"/>
       <c r="I8" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J8" s="31"/>
       <c r="K8" s="30"/>
       <c r="L8" s="31" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M8" s="31"/>
       <c r="N8" s="30"/>
       <c r="O8" s="31" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="30"/>
       <c r="R8" s="31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="S8" s="31"/>
       <c r="T8" s="30"/>
       <c r="U8" s="31" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="V8" s="31"/>
       <c r="W8" s="30"/>
       <c r="X8" s="31" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Y8" s="31"/>
       <c r="Z8" s="32"/>
@@ -9425,42 +9502,42 @@
     <row r="9" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="29"/>
       <c r="C9" s="31" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="31"/>
       <c r="E9" s="30"/>
       <c r="F9" s="31" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G9" s="31"/>
       <c r="H9" s="30"/>
       <c r="I9" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J9" s="31"/>
       <c r="K9" s="30"/>
       <c r="L9" s="31" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M9" s="31"/>
       <c r="N9" s="30"/>
       <c r="O9" s="31" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P9" s="31"/>
       <c r="Q9" s="30"/>
       <c r="R9" s="31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="S9" s="31"/>
       <c r="T9" s="30"/>
       <c r="U9" s="31" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="V9" s="31"/>
       <c r="W9" s="30"/>
       <c r="X9" s="31" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Y9" s="31"/>
       <c r="Z9" s="32"/>
@@ -9468,42 +9545,42 @@
     <row r="10" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="29"/>
       <c r="C10" s="31" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D10" s="31"/>
       <c r="E10" s="30"/>
       <c r="F10" s="31" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G10" s="31"/>
       <c r="H10" s="30"/>
       <c r="I10" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J10" s="31"/>
       <c r="K10" s="30"/>
       <c r="L10" s="31" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M10" s="31"/>
       <c r="N10" s="30"/>
       <c r="O10" s="31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P10" s="31"/>
       <c r="Q10" s="30"/>
       <c r="R10" s="31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="S10" s="31"/>
       <c r="T10" s="30"/>
       <c r="U10" s="31" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="V10" s="31"/>
       <c r="W10" s="30"/>
       <c r="X10" s="31" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Y10" s="31"/>
       <c r="Z10" s="32"/>
@@ -9511,42 +9588,42 @@
     <row r="11" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="29"/>
       <c r="C11" s="31" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="30"/>
       <c r="F11" s="31" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G11" s="31"/>
       <c r="H11" s="30"/>
       <c r="I11" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J11" s="31"/>
       <c r="K11" s="30"/>
       <c r="L11" s="31" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M11" s="31"/>
       <c r="N11" s="30"/>
       <c r="O11" s="31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P11" s="31"/>
       <c r="Q11" s="30"/>
       <c r="R11" s="31" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="S11" s="31"/>
       <c r="T11" s="30"/>
       <c r="U11" s="31" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="V11" s="31"/>
       <c r="W11" s="30"/>
       <c r="X11" s="31" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Y11" s="31"/>
       <c r="Z11" s="32"/>
@@ -9554,42 +9631,42 @@
     <row r="12" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="29"/>
       <c r="C12" s="31" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="30"/>
       <c r="F12" s="31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G12" s="31"/>
       <c r="H12" s="30"/>
       <c r="I12" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J12" s="31"/>
       <c r="K12" s="30"/>
       <c r="L12" s="31" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M12" s="31"/>
       <c r="N12" s="30"/>
       <c r="O12" s="31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P12" s="31"/>
       <c r="Q12" s="30"/>
       <c r="R12" s="31" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="30"/>
       <c r="U12" s="31" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="V12" s="31"/>
       <c r="W12" s="30"/>
       <c r="X12" s="31" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Y12" s="31"/>
       <c r="Z12" s="32"/>
@@ -9597,42 +9674,42 @@
     <row r="13" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="29"/>
       <c r="C13" s="31" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D13" s="31"/>
       <c r="E13" s="30"/>
       <c r="F13" s="31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G13" s="31"/>
       <c r="H13" s="30"/>
       <c r="I13" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J13" s="31"/>
       <c r="K13" s="30"/>
       <c r="L13" s="31" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M13" s="31"/>
       <c r="N13" s="30"/>
       <c r="O13" s="31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P13" s="31"/>
       <c r="Q13" s="30"/>
       <c r="R13" s="31" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="S13" s="31"/>
       <c r="T13" s="30"/>
       <c r="U13" s="31" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="V13" s="31"/>
       <c r="W13" s="30"/>
       <c r="X13" s="31" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Y13" s="31"/>
       <c r="Z13" s="32"/>
@@ -9640,42 +9717,42 @@
     <row r="14" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="29"/>
       <c r="C14" s="31" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="30"/>
       <c r="F14" s="31" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G14" s="31"/>
       <c r="H14" s="30"/>
       <c r="I14" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J14" s="31"/>
       <c r="K14" s="30"/>
       <c r="L14" s="31" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M14" s="31"/>
       <c r="N14" s="30"/>
       <c r="O14" s="31" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P14" s="31"/>
       <c r="Q14" s="30"/>
       <c r="R14" s="31" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="S14" s="31"/>
       <c r="T14" s="30"/>
       <c r="U14" s="31" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="V14" s="31"/>
       <c r="W14" s="30"/>
       <c r="X14" s="31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Y14" s="31"/>
       <c r="Z14" s="32"/>
@@ -9683,42 +9760,42 @@
     <row r="15" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29"/>
       <c r="C15" s="31" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D15" s="31"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="30"/>
       <c r="I15" s="31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J15" s="31"/>
       <c r="K15" s="30"/>
       <c r="L15" s="31" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M15" s="31"/>
       <c r="N15" s="30"/>
       <c r="O15" s="31" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P15" s="31"/>
       <c r="Q15" s="30"/>
       <c r="R15" s="31" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="S15" s="31"/>
       <c r="T15" s="30"/>
       <c r="U15" s="31" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="V15" s="31"/>
       <c r="W15" s="30"/>
       <c r="X15" s="31" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Y15" s="31"/>
       <c r="Z15" s="32"/>
@@ -9957,14 +10034,14 @@
         <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -9975,7 +10052,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -9984,7 +10063,9 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="47"/>
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>74</v>
       </c>
@@ -9993,7 +10074,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -10004,7 +10085,9 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="46"/>
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
@@ -10013,7 +10096,9 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47"/>
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>74</v>
       </c>
@@ -10022,7 +10107,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -10033,7 +10118,9 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
@@ -10042,7 +10129,9 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47"/>
+      <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>74</v>
       </c>
@@ -10051,7 +10140,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -10062,7 +10151,9 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
@@ -10071,7 +10162,9 @@
       </c>
     </row>
     <row r="15" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="47"/>
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>74</v>
       </c>
@@ -10091,7 +10184,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="46" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -10102,7 +10195,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="47"/>
+      <c r="A18" s="48"/>
       <c r="B18" s="2" t="s">
         <v>74</v>
       </c>
@@ -10137,7 +10230,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>62</v>
@@ -10148,18 +10241,14 @@
         <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
+  <mergeCells count="1">
     <mergeCell ref="A17:A18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -10179,15 +10268,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C2"/>
     </row>
@@ -10209,7 +10298,7 @@
       </c>
       <c r="C4"/>
     </row>
-    <row r="5" spans="1:3" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
@@ -10250,579 +10339,581 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="B2" s="16"/>
+        <v>339</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>490</v>
+      </c>
       <c r="C2" s="16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="H8"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27"/>
@@ -10863,34 +10954,34 @@
         <v>64</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
-        <v>470</v>
-      </c>
-      <c r="B3" s="54" t="s">
+        <v>469</v>
+      </c>
+      <c r="B3" s="55" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="B4" s="55"/>
+        <v>470</v>
+      </c>
+      <c r="B4" s="56"/>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>471</v>
+      </c>
+      <c r="B5" s="56"/>
     </row>
     <row r="6" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="B6" s="56"/>
+        <v>472</v>
+      </c>
+      <c r="B6" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10919,10 +11010,10 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>124</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>125</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>69</v>
@@ -10930,7 +11021,7 @@
       <c r="E2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B3" s="2">
@@ -10943,7 +11034,9 @@
       <c r="E3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
+      <c r="A4" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="B4" s="2">
         <v>102</v>
       </c>
@@ -10954,7 +11047,7 @@
       <c r="E4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B5" s="2">
@@ -10967,7 +11060,9 @@
       <c r="E5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="51"/>
+      <c r="A6" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B6" s="2">
         <v>802</v>
       </c>
@@ -10978,7 +11073,9 @@
       <c r="E6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="51"/>
+      <c r="A7" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B7" s="2">
         <v>803</v>
       </c>
@@ -10989,7 +11086,9 @@
       <c r="E7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="51"/>
+      <c r="A8" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B8" s="2">
         <v>804</v>
       </c>
@@ -11000,7 +11099,9 @@
       <c r="E8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
+      <c r="A9" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B9" s="2">
         <v>805</v>
       </c>
@@ -11011,7 +11112,9 @@
       <c r="E9"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="51"/>
+      <c r="A10" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B10" s="2">
         <v>806</v>
       </c>
@@ -11022,7 +11125,9 @@
       <c r="E10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="51"/>
+      <c r="A11" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B11" s="2">
         <v>807</v>
       </c>
@@ -11033,7 +11138,9 @@
       <c r="E11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="51"/>
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B12" s="2">
         <v>808</v>
       </c>
@@ -11044,7 +11151,9 @@
       <c r="E12"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="51"/>
+      <c r="A13" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B13" s="2">
         <v>809</v>
       </c>
@@ -11055,7 +11164,7 @@
       <c r="E13"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B14" s="2">
@@ -11068,7 +11177,9 @@
       <c r="E14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="51"/>
+      <c r="A15" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B15" s="2">
         <v>902</v>
       </c>
@@ -11079,7 +11190,9 @@
       <c r="E15"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="51"/>
+      <c r="A16" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B16" s="2">
         <v>903</v>
       </c>
@@ -11090,7 +11203,9 @@
       <c r="E16"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
+      <c r="A17" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B17" s="2">
         <v>904</v>
       </c>
@@ -11101,7 +11216,9 @@
       <c r="E17"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="51"/>
+      <c r="A18" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B18" s="2">
         <v>905</v>
       </c>
@@ -11112,7 +11229,9 @@
       <c r="E18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
+      <c r="A19" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B19" s="2">
         <v>906</v>
       </c>
@@ -11123,7 +11242,9 @@
       <c r="E19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="51"/>
+      <c r="A20" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B20" s="2">
         <v>907</v>
       </c>
@@ -11134,7 +11255,9 @@
       <c r="E20"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="51"/>
+      <c r="A21" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B21" s="2">
         <v>908</v>
       </c>
@@ -11145,7 +11268,9 @@
       <c r="E21"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
+      <c r="A22" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B22" s="2">
         <v>909</v>
       </c>
@@ -11156,7 +11281,7 @@
       <c r="E22"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B23" s="2">
@@ -11169,7 +11294,9 @@
       <c r="E23"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="51"/>
+      <c r="A24" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B24" s="2">
         <v>1002</v>
       </c>
@@ -11180,7 +11307,9 @@
       <c r="E24"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
+      <c r="A25" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B25" s="2">
         <v>1003</v>
       </c>
@@ -11191,7 +11320,9 @@
       <c r="E25"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="51"/>
+      <c r="A26" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B26" s="2">
         <v>1004</v>
       </c>
@@ -11202,7 +11333,9 @@
       <c r="E26"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="51"/>
+      <c r="A27" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B27" s="2">
         <v>1005</v>
       </c>
@@ -11213,7 +11346,9 @@
       <c r="E27"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="51"/>
+      <c r="A28" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B28" s="2">
         <v>1006</v>
       </c>
@@ -11224,7 +11359,9 @@
       <c r="E28"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="51"/>
+      <c r="A29" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B29" s="2">
         <v>1007</v>
       </c>
@@ -11235,7 +11372,9 @@
       <c r="E29"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="51"/>
+      <c r="A30" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B30" s="2">
         <v>1008</v>
       </c>
@@ -11246,7 +11385,9 @@
       <c r="E30"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="51"/>
+      <c r="A31" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B31" s="2">
         <v>1009</v>
       </c>
@@ -11257,7 +11398,7 @@
       <c r="E31"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="51" t="s">
+      <c r="A32" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B32" s="2">
@@ -11270,7 +11411,9 @@
       <c r="E32"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="51"/>
+      <c r="A33" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B33" s="2">
         <v>1102</v>
       </c>
@@ -11281,7 +11424,9 @@
       <c r="E33"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="51"/>
+      <c r="A34" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B34" s="2">
         <v>1103</v>
       </c>
@@ -11292,7 +11437,9 @@
       <c r="E34"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="51"/>
+      <c r="A35" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B35" s="2">
         <v>1104</v>
       </c>
@@ -11303,7 +11450,9 @@
       <c r="E35"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="51"/>
+      <c r="A36" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B36" s="2">
         <v>1105</v>
       </c>
@@ -11314,7 +11463,9 @@
       <c r="E36"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="51"/>
+      <c r="A37" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B37" s="2">
         <v>1106</v>
       </c>
@@ -11325,7 +11476,9 @@
       <c r="E37"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="51"/>
+      <c r="A38" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B38" s="2">
         <v>1107</v>
       </c>
@@ -11336,7 +11489,9 @@
       <c r="E38"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="51"/>
+      <c r="A39" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B39" s="2">
         <v>1108</v>
       </c>
@@ -11347,7 +11502,9 @@
       <c r="E39"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="51"/>
+      <c r="A40" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B40" s="2">
         <v>1109</v>
       </c>
@@ -11358,7 +11515,7 @@
       <c r="E40"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="51" t="s">
+      <c r="A41" s="3" t="s">
         <v>122</v>
       </c>
       <c r="B41" s="2">
@@ -11371,7 +11528,9 @@
       <c r="E41"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="51"/>
+      <c r="A42" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B42" s="2">
         <v>1203</v>
       </c>
@@ -11382,9 +11541,11 @@
       <c r="E42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="51"/>
+      <c r="A43" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B43" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C43" s="2">
         <v>20</v>
@@ -11393,7 +11554,9 @@
       <c r="E43"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="51"/>
+      <c r="A44" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B44" s="2">
         <v>1204</v>
       </c>
@@ -11404,7 +11567,9 @@
       <c r="E44"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="51"/>
+      <c r="A45" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B45" s="2">
         <v>1205</v>
       </c>
@@ -11415,7 +11580,9 @@
       <c r="E45"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="51"/>
+      <c r="A46" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B46" s="2">
         <v>1206</v>
       </c>
@@ -11426,7 +11593,9 @@
       <c r="E46"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="51"/>
+      <c r="A47" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B47" s="2">
         <v>1207</v>
       </c>
@@ -11437,7 +11606,9 @@
       <c r="E47"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="51"/>
+      <c r="A48" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B48" s="2">
         <v>1208</v>
       </c>
@@ -11448,7 +11619,9 @@
       <c r="E48"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="51"/>
+      <c r="A49" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="B49" s="2">
         <v>1209</v>
       </c>
@@ -11469,14 +11642,6 @@
       <c r="E50"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A41:A49"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="A23:A31"/>
-    <mergeCell ref="A32:A40"/>
-  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11487,13 +11652,14 @@
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="12.625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="12.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.625" style="1" customWidth="1"/>
     <col min="4" max="10" width="20.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -11501,35 +11667,35 @@
         <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>133</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>134</v>
       </c>
       <c r="I2" s="16"/>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -11541,9 +11707,11 @@
       <c r="J3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
+      <c r="A4" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B4" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -11555,9 +11723,11 @@
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="51"/>
+      <c r="A5" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B5" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -11569,9 +11739,11 @@
       <c r="J5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="51"/>
+      <c r="A6" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="B6" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -11583,11 +11755,11 @@
       <c r="J6"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -11599,9 +11771,11 @@
       <c r="J7"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="51"/>
+      <c r="A8" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B8" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -11613,9 +11787,11 @@
       <c r="J8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
+      <c r="A9" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B9" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -11627,9 +11803,11 @@
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="51"/>
+      <c r="A10" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="B10" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -11641,11 +11819,11 @@
       <c r="J10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -11657,9 +11835,11 @@
       <c r="J11"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="51"/>
+      <c r="A12" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B12" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -11671,9 +11851,11 @@
       <c r="J12"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="51"/>
+      <c r="A13" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="B13" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -11685,11 +11867,11 @@
       <c r="J13"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -11701,9 +11883,11 @@
       <c r="J14"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="51"/>
+      <c r="A15" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B15" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -11715,9 +11899,11 @@
       <c r="J15"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="51"/>
+      <c r="A16" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="B16" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -11729,11 +11915,11 @@
       <c r="J16"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -11745,9 +11931,11 @@
       <c r="J17"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="51"/>
+      <c r="A18" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="B18" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -11759,9 +11947,11 @@
       <c r="J18"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
+      <c r="A19" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="B19" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -11774,7 +11964,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="2"/>
@@ -11788,7 +11978,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="2"/>
@@ -11831,13 +12021,6 @@
       <c r="J22"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A19"/>
-  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11860,33 +12043,33 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C2" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>163</v>
-      </c>
       <c r="H2" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I2"/>
     </row>
@@ -11895,17 +12078,17 @@
         <v>107</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G3" s="20">
         <v>1</v>
@@ -11918,17 +12101,17 @@
         <v>107</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G4" s="20">
         <v>2</v>
@@ -11941,17 +12124,17 @@
         <v>107</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" s="20"/>
       <c r="E5" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G5" s="20">
         <v>3</v>
@@ -11964,17 +12147,17 @@
         <v>107</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D6" s="20"/>
       <c r="E6" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G6" s="20">
         <v>4</v>
@@ -11987,14 +12170,14 @@
         <v>107</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F7" s="20">
         <v>1200</v>
@@ -12010,14 +12193,14 @@
         <v>107</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F8" s="20">
         <v>2100</v>
@@ -12033,14 +12216,14 @@
         <v>107</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F9" s="20">
         <v>2100</v>
@@ -12056,14 +12239,14 @@
         <v>107</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="20">
@@ -12077,14 +12260,14 @@
         <v>107</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20">
@@ -12098,14 +12281,14 @@
         <v>107</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20">
@@ -12119,17 +12302,17 @@
         <v>108</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G13" s="2">
         <v>15</v>
@@ -12142,17 +12325,17 @@
         <v>108</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G14" s="2">
         <v>4</v>
@@ -12165,14 +12348,14 @@
         <v>108</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2">
@@ -12186,14 +12369,14 @@
         <v>108</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2">
@@ -12207,17 +12390,17 @@
         <v>108</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G17" s="2">
         <v>17</v>
@@ -12230,17 +12413,17 @@
         <v>108</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
@@ -12253,17 +12436,17 @@
         <v>108</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
@@ -12276,14 +12459,14 @@
         <v>108</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2">
@@ -12297,14 +12480,14 @@
         <v>108</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2">
@@ -12318,14 +12501,14 @@
         <v>108</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2">
